--- a/Schedule_results.xlsx
+++ b/Schedule_results.xlsx
@@ -619,179 +619,179 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Lísa</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Unnur</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pétur</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Aron</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Thelma</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Helgi</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Vala</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Úlfur</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Davíð</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Helgi</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Ásdís</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Ásdís</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Oliver</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Helgi</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>Harpa</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Rakel</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Vala</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Harpa</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Inga</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Thelma</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Úlfur</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Unnur</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Pétur</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Oliver</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Ásdís</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Jóna</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Erla</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Ásdís</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Helgi</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Gunnar</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Harpa</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Laufey</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Lísa</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Ásdís</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Helgi</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Kata</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Harpa</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Pétur</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Thelma</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Freyja</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Bergur</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Ásdís</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Nanna</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Ásdís</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Máni</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Kata</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Helgi</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Oliver</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Thelma</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Sara</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Ásdís</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Inga</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Davíð</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Ylfa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Oliver</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Aron</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kata</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Laufey</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Nanna</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Camilla</t>
+          <t>Harpa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -802,14 +802,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Máni</t>
+          <t>Jóna</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Thelma</t>
+          <t>Unnur</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -820,36 +820,36 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Thelma</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Unnur</t>
+          <t>Freyja</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Jóna</t>
+          <t>Silja</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Thelma</t>
+          <t>Pétur</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Pétur</t>
+          <t>Freyja</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Ylfa</t>
+          <t>Bergur</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -859,24 +859,24 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Nanna</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Aron</t>
+          <t>Laufey</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Helgi</t>
+          <t>Össur</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Gunnar</t>
         </is>
       </c>
     </row>
@@ -890,13 +890,13 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nanna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Unnur</t>
+          <t>Pétur</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -905,18 +905,18 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Vala</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Pétur</t>
+          <t>Freyja</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Laufey</t>
+          <t>Vala</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -929,32 +929,32 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Vala</t>
+          <t>Unnur</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Vala</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Unnur</t>
+          <t>Thelma</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Össur</t>
+          <t>Thelma</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -968,7 +968,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lísa</t>
+          <t>Harpa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -982,13 +982,13 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Unnur</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Máni</t>
+          <t>Erla</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1001,20 +1001,20 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Freyja</t>
+          <t>Vala</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Freyja</t>
+          <t>Lísa</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Freyja</t>
+          <t>Unnur</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Pétur</t>
+          <t>Freyja</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1036,7 +1036,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Davíð</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1045,18 +1045,18 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Rakel</t>
+          <t>Davíð</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Máni</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Davíð</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1069,20 +1069,20 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Lísa</t>
+          <t>Rakel</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Rakel</t>
+          <t>Lísa</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1090,7 +1090,7 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Harpa</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Rakel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1113,23 +1113,23 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Laufey</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Erla</t>
+          <t>Inga</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Ylfa</t>
+          <t>Úlfur</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Úlfur</t>
+          <t>Laufey</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1137,20 +1137,20 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Rakel</t>
+          <t>Lísa</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Erla</t>
+          <t>Laufey</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Davíð</t>
+          <t>Erla</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1158,7 +1158,7 @@
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Vala</t>
+          <t>Rakel</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Úlfur</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1181,23 +1181,23 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Inga</t>
+          <t>Ylfa</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Davíð</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Jóna</t>
+          <t>Inga</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Jóna</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1205,7 +1205,7 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Kata</t>
+          <t>Aron</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aron</t>
+          <t>Máni</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1226,7 +1226,7 @@
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1249,23 +1249,23 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Nanna</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Laufey</t>
+          <t>Kata</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Nanna</t>
+          <t>Jóna</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Silja</t>
+          <t>Máni</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1273,20 +1273,20 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Camilla</t>
+          <t>Úlfur</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Inga</t>
+          <t>Kata</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Ylfa</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Erla</t>
+          <t>Inga</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1308,7 +1308,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Inga</t>
+          <t>Jóna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1317,23 +1317,23 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Kata</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Úlfur</t>
+          <t>Nanna</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Silja</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Camilla</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1341,7 +1341,7 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Nanna</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1354,7 +1354,7 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ylfa</t>
+          <t>Silja</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1362,7 +1362,7 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Davíð</t>
+          <t>Kata</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1376,7 +1376,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jóna</t>
+          <t>Camilla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1385,23 +1385,23 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Ylfa</t>
+          <t>Bergur</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Silja</t>
+          <t>Ólafur</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Bergur</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Ólafur</t>
+          <t>Kata</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1409,7 +1409,7 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ylfa</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1422,7 +1422,7 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Silja</t>
+          <t>Ólafur</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1430,7 +1430,7 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Úlfur</t>
+          <t>Camilla</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -1453,12 +1453,12 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Camilla</t>
+          <t>Gunnar</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ólafur</t>
+          <t>Bergur</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Bergur</t>
+          <t>Camilla</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1477,20 +1477,20 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Gunnar</t>
+          <t>Bergur</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Bergur</t>
+          <t>Camilla</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ólafur</t>
+          <t>Bergur</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -1498,7 +1498,7 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Camilla</t>
+          <t>Ólafur</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -1683,790 +1683,790 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>MúsikTilraunir
+2024-05-02 19:00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MúsikTilraunir
+2024-05-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-09 18:30:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sígildir
+2024-05-05 16:00:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Gusgus
 2024-05-11 20:00:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ABBA
+2024-05-10 19:00:00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MúsikTilraunir
+2024-05-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MúsikTilraunir
+2024-05-03 19:00:00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ABBA
+2024-05-10 19:00:00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ABBA
+2024-05-10 19:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ABBA
+2024-05-10 19:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-09 18:30:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Upprás
 2024-05-01 15:00:00</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>MúsikTilraunir
+2024-05-02 19:00:00</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>How to 
+2024-05-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>MúsikTilraunir
+2024-05-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>Gusgus
 2024-05-11 20:00:00</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>MúsikTilraunir
+2024-05-03 19:00:00</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>How to 
+2024-05-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>How to 
+2024-05-04 18:00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Upprás
+2024-05-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-09 18:30:00</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>K&amp;B
+2024-05-05 12:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-09 18:30:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MúsikTilraunir
+2024-05-02 19:00:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ABBA
+2024-05-10 19:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Vitringar
 2024-05-12 18:00:00</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MúsikTilraunir
-2024-05-03 19:00:00</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vitringar
+2024-05-12 18:00:00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-09 18:30:00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vitringar
+2024-05-12 18:00:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vitringar
+2024-05-12 18:00:00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-09 18:30:00</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Krakka Sinfó
 2024-05-04 14:00:00</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Vitringar
+2024-05-12 18:00:00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Múlinn
+2024-05-08 19:00:00</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Gusgus
+2024-05-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>K&amp;B
+2024-05-05 12:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Vitringar
+2024-05-12 18:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vitringar
+2024-05-12 18:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-09 18:30:00</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>ABBA
 2024-05-10 19:00:00</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-09 18:30:00</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-09 18:30:00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Vitringar
+2024-05-12 18:00:00</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>ABBA
+2024-05-10 19:00:00</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>Fatahengi
 2024-05-13 18:30:00</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>MúsikTilraunir
-2024-05-01 19:00:00</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>MúsikTilraunir
-2024-05-02 19:00:00</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>MúsikTilraunir
-2024-05-02 19:00:00</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-04 14:00:00</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-04 14:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-04 14:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>How to 
-2024-05-01 19:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>MúsikTilraunir
-2024-05-01 19:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-04 14:00:00</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-04 14:00:00</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>MúsikTilraunir
-2024-05-02 19:00:00</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>MúsikTilraunir
-2024-05-01 19:00:00</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Gusgus
+2024-05-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-09 18:30:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Gusgus
+2024-05-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-09 18:30:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>ABBA
 2024-05-10 19:00:00</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>MúsikTilraunir
-2024-05-03 19:00:00</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-04 14:00:00</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>ABBA
 2024-05-10 19:00:00</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-09 18:30:00</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-04 14:00:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Upprás
-2024-05-01 15:00:00</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-09 18:30:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>How to 
-2024-05-01 19:00:00</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-04 14:00:00</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-04 14:00:00</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-04 14:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>ABBA
+2024-05-10 19:00:00</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Gusgus
+2024-05-11 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gusgus
+2024-05-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Sinfó
 2024-05-16 18:30:00</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-16 18:30:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Abba
 2024-05-18 10:00:00</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Abba
+2024-05-18 10:00:00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gusgus
+2024-05-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-20 16:00:00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Abba
+2024-05-18 10:00:00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Gusgus
+2024-05-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Vitringar
 2024-05-12 18:00:00</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Sinfó
 2024-05-16 18:30:00</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Gusgus
+2024-05-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Fatahengi
+2024-05-14 18:30:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Gusgus
+2024-05-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Abba
+2024-05-18 10:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Abba
+2024-05-18 10:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Sinfó
-2024-05-09 18:30:00</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+2024-05-16 18:30:00</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Vitringar
+2024-05-12 18:00:00</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>ABBA
 2024-05-10 19:00:00</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>How to 
+2024-05-11 16:00:00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-16 18:30:00</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Abba
+2024-05-18 10:00:00</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>Vitringar
 2024-05-12 18:00:00</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Abba
+2024-05-18 10:00:00</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Sinfó
 2024-05-16 18:30:00</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>How to 
-2024-05-04 18:00:00</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>K&amp;B
-2024-05-05 12:00:00</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Sinfó
-2024-05-09 18:30:00</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>ABBA
-2024-05-10 19:00:00</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-09 18:30:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Gusgus
-2024-05-11 20:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-09 18:30:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Sígildir
-2024-05-05 16:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Múlinn
-2024-05-08 19:00:00</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>K&amp;B
-2024-05-05 12:00:00</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Gusgus
-2024-05-11 20:00:00</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>ABBA
-2024-05-10 19:00:00</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Vitringar
-2024-05-12 18:00:00</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-09 18:30:00</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-09 18:30:00</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Vitringar
-2024-05-12 18:00:00</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+2024-05-16 18:30:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Sígildir
 2024-05-12 19:00:00</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>ABBA
-2024-05-10 19:00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Sinfó
-2024-05-09 18:30:00</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Gusgus
-2024-05-11 20:00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
+2024-05-16 18:30:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-20 16:00:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-20 16:00:00</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-20 16:00:00</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>Sinfó
-2024-05-09 18:30:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>ABBA
-2024-05-10 19:00:00</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>ABBA
-2024-05-10 19:00:00</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>ABBA
-2024-05-10 19:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+2024-05-16 18:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Fatahengi
+2024-05-24 20:00:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Abba
+2024-05-18 10:00:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Upprás
+2024-05-19 20:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-26 10:00:00</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-26 10:00:00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fatahengi
+2024-05-31 18:00:00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fatahengi
+2024-05-24 20:00:00</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-26 10:00:00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Fatahengi
+2024-05-31 18:00:00</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fatahengi
+2024-05-13 18:30:00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Múlinn
+2024-05-30 17:00:00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-26 10:00:00</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-26 10:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Maxi
 2024-05-23 15:00:00</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-20 16:00:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-26 10:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Fatahengi
-2024-05-14 18:30:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-26 10:00:00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Vitringar
-2024-05-12 18:00:00</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-20 16:00:00</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+2024-05-24 20:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Abba
 2024-05-18 10:00:00</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-20 16:00:00</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Maxi
+2024-05-23 15:00:00</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-16 18:30:00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sígildir
+2024-05-19 12:00:00</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-26 10:00:00</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-26 10:00:00</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-20 16:00:00</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-20 16:00:00</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Abba
 2024-05-18 10:00:00</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Gusgus
-2024-05-11 20:00:00</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Gusgus
-2024-05-11 20:00:00</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Gusgus
-2024-05-11 20:00:00</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-20 16:00:00</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Sinfó
+2024-05-16 18:30:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Abba
 2024-05-18 10:00:00</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Vitringar
-2024-05-12 18:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>How to 
-2024-05-11 16:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>ABBA
-2024-05-10 19:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-09 18:30:00</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Gusgus
-2024-05-11 20:00:00</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-16 18:30:00</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Gusgus
-2024-05-11 20:00:00</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Abba
-2024-05-18 10:00:00</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Vitringar
-2024-05-12 18:00:00</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-20 16:00:00</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Abba
-2024-05-18 10:00:00</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-16 18:30:00</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Vitringar
-2024-05-12 18:00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-16 18:30:00</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Abba
-2024-05-18 10:00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-16 18:30:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Vitringar
-2024-05-12 18:00:00</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-20 16:00:00</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Vitringar
-2024-05-12 18:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Fatahengi
-2024-05-31 18:00:00</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Fatahengi
-2024-05-24 20:00:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Abba
-2024-05-18 10:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Fatahengi
-2024-05-31 18:00:00</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-16 18:30:00</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Múlinn
+2024-05-25 13:00:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Krakka Sinfó
 2024-05-26 10:00:00</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Krakka Sinfó
 2024-05-26 10:00:00</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-20 16:00:00</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-16 18:30:00</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-26 10:00:00</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Fatahengi
-2024-05-24 20:00:00</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-26 10:00:00</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Múlinn
-2024-05-30 17:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Fatahengi
-2024-05-13 18:30:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-16 18:30:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Gusgus
-2024-05-11 20:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Abba
-2024-05-18 10:00:00</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Sígildir
-2024-05-19 12:00:00</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>How to 
 2024-05-17 19:00:00</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Maxi
-2024-05-23 15:00:00</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-26 10:00:00</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Sinfó
-2024-05-16 18:30:00</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Múlinn
-2024-05-25 13:00:00</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-20 16:00:00</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Fatahengi
-2024-05-24 20:00:00</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-20 16:00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Abba
-2024-05-18 10:00:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Upprás
-2024-05-19 20:00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Abba
-2024-05-18 10:00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-20 16:00:00</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-26 10:00:00</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-26 10:00:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-20 16:00:00</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-26 10:00:00</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -2476,46 +2476,46 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-20 16:00:00</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
         <is>
           <t>Upprás
 2024-05-19 20:00:00</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-20 16:00:00</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Krakka Sinfó
 2024-05-26 10:00:00</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Krakka Sinfó
+2024-05-20 16:00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
           <t>Krakka Sinfó
 2024-05-20 16:00:00</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Krakka Sinfó
-2024-05-26 10:00:00</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ásdís, Kata</t>
+          <t>Unnur, Oliver</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oliver, Laufey, Gunnar</t>
+          <t>Pétur, Aron, Gunnar</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vala, Aron</t>
+          <t>Lísa, Ylfa</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Harpa, Helena, Nanna</t>
+          <t>Aron, Nanna, Anna</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rakel, Camilla</t>
+          <t>Thelma, Harpa</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gunnar</t>
+          <t>Vala</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Helgi, Össur, Unnur, Lísa, Davíð, Sara, Úlfur, Máni, Inga, Jóna, Ólafur</t>
+          <t>Helgi, Össur, Pétur, Harpa, Björk, Rakel, Sara, Máni, Jóna, Camilla, Ólafur</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Harpa, Máni</t>
+          <t>Úlfur, Jóna</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Laufey</t>
+          <t>Davíð</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lísa</t>
+          <t>Helgi</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ásdís, Thelma, Vala, Lísa, Rakel, Sara, Inga, Helena, Kata, Ylfa, Camilla</t>
+          <t>Ásdís, Unnur, Oliver, Lísa, Davíð, Laufey, Ylfa, Nanna, Anna, Bergur, Gunnar</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Helgi, Össur, Pétur, Unnur, Oliver, Erla, Davíð, Laufey, Úlfur, Silja, Ólafur</t>
+          <t>Ásdís, Össur, Freyja, Sara, Máni, Inga, Helena, Kata, Nanna, Ólafur, Bergur</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Harpa, Oliver, Laufey, Máni, Helena, Ylfa, Jóna, Nanna, Anna, Bergur, Gunnar</t>
+          <t>Helgi, Thelma, Vala, Erla, Davíð, Úlfur, Inga, Jóna, Silja, Anna, Gunnar</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kata</t>
+          <t>Oliver</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thelma</t>
+          <t>Vala</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pétur, Unnur, Björk, Erla, Rakel, Úlfur, Jóna, Silja, Camilla, Ólafur, Bergur</t>
+          <t>Harpa, Freyja, Björk, Erla, Rakel, Laufey, Sara, Máni, Helena, Kata, Camilla</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Freyja, Jóna</t>
+          <t>Harpa, Silja</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bergur</t>
+          <t>Inga</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ásdís, Thelma, Vala, Freyja, Björk, Rakel, Kata, Camilla, Nanna, Anna, Gunnar</t>
+          <t>Thelma, Pétur, Unnur, Vala, Oliver, Lísa, Aron, Úlfur, Helena, Ylfa, Bergur</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nanna</t>
+          <t>Úlfur</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ásdís, Pétur, Vala, Freyja, Lísa, Erla, Aron, Inga, Ylfa, Silja, Bergur</t>
+          <t>Unnur, Freyja, Björk, Lísa, Rakel, Laufey, Aron, Kata, Ylfa, Silja, Camilla</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Máni</t>
+          <t>Pétur</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kata, Ylfa</t>
+          <t>Oliver, Bergur</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Helgi, Össur, Unnur, Freyja, Rakel, Davíð, Aron, Sara, Ylfa, Silja, Ólafur</t>
+          <t>Ásdís, Össur, Thelma, Unnur, Lísa, Erla, Máni, Ylfa, Silja, Ólafur, Bergur</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oliver, Anna</t>
+          <t>Jóna, Nanna</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thelma, Aron, Helena</t>
+          <t>Erla, Laufey, Anna</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Ásdís</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ásdís, Helgi, Össur, Pétur, Harpa, Vala, Björk, Erla, Davíð, Úlfur, Camilla</t>
+          <t>Helgi, Össur, Thelma, Freyja, Björk, Rakel, Sara, Inga, Kata, Camilla, Ólafur</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inga</t>
+          <t>Helena</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Björk, Anna</t>
+          <t>Davíð, Gunnar</t>
         </is>
       </c>
     </row>
